--- a/MaestraPLU_PPreparados.xlsx
+++ b/MaestraPLU_PPreparados.xlsx
@@ -433,7 +433,7 @@
         <v>20106</v>
       </c>
       <c r="E2" t="str">
-        <v>3290</v>
+        <v>5990</v>
       </c>
       <c r="F2" t="str">
         <v>Por cantidad</v>
@@ -493,7 +493,7 @@
         <v>20103</v>
       </c>
       <c r="E5" t="str">
-        <v>3290</v>
+        <v>5990</v>
       </c>
       <c r="F5" t="str">
         <v>Por cantidad</v>
@@ -593,7 +593,7 @@
         <v>20190</v>
       </c>
       <c r="E10" t="str">
-        <v>3290</v>
+        <v>5990</v>
       </c>
       <c r="F10" t="str">
         <v>Por cantidad</v>
@@ -613,7 +613,7 @@
         <v>20180</v>
       </c>
       <c r="E11" t="str">
-        <v>3290</v>
+        <v>5990</v>
       </c>
       <c r="F11" t="str">
         <v>Por cantidad</v>
@@ -953,7 +953,7 @@
         <v>20170</v>
       </c>
       <c r="E28" t="str">
-        <v>3290</v>
+        <v>5990</v>
       </c>
       <c r="F28" t="str">
         <v>Por cantidad</v>

--- a/MaestraPLU_PPreparados.xlsx
+++ b/MaestraPLU_PPreparados.xlsx
@@ -624,7 +624,7 @@
         <v>531206</v>
       </c>
       <c r="B12" t="str">
-        <v>COSTILLAR BBQ CON PURE</v>
+        <v>COSTILLAR CON PURE</v>
       </c>
       <c r="C12" t="str">
         <v/>
